--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N72_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N72_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.42531884206708</v>
+        <v>1.0441143118359</v>
       </c>
       <c r="D2" t="n">
-        <v>58.05179443386946</v>
+        <v>9.433416595503788</v>
       </c>
       <c r="E2" t="n">
-        <v>23.12722433264445</v>
+        <v>3.758173954054723</v>
       </c>
       <c r="F2" t="n">
-        <v>12.18150384974995</v>
+        <v>1.979494375584367</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.50666913981952</v>
+        <v>11.45733373522067</v>
       </c>
       <c r="D3" t="n">
-        <v>71.77628294241015</v>
+        <v>11.66364597814165</v>
       </c>
       <c r="E3" t="n">
-        <v>23.12722433264445</v>
+        <v>3.758173954054723</v>
       </c>
       <c r="F3" t="n">
-        <v>12.18150384974995</v>
+        <v>1.979494375584367</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>68.19932021266646</v>
+        <v>11.0823895345583</v>
       </c>
       <c r="D4" t="n">
-        <v>69.66726359806086</v>
+        <v>11.32093033468489</v>
       </c>
       <c r="E4" t="n">
-        <v>23.12722433264445</v>
+        <v>3.758173954054723</v>
       </c>
       <c r="F4" t="n">
-        <v>12.18150384974995</v>
+        <v>1.979494375584367</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.90861652125272</v>
+        <v>6.810150184703567</v>
       </c>
       <c r="D5" t="n">
-        <v>41.55937214851404</v>
+        <v>6.753397974133533</v>
       </c>
       <c r="E5" t="n">
-        <v>23.12722433264445</v>
+        <v>3.758173954054723</v>
       </c>
       <c r="F5" t="n">
-        <v>12.18150384974995</v>
+        <v>1.979494375584367</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>46.07866400203539</v>
+        <v>7.487782900330751</v>
       </c>
       <c r="D6" t="n">
-        <v>45.84866010299137</v>
+        <v>7.450407266736097</v>
       </c>
       <c r="E6" t="n">
-        <v>23.12722433264445</v>
+        <v>3.758173954054723</v>
       </c>
       <c r="F6" t="n">
-        <v>12.18150384974995</v>
+        <v>1.979494375584367</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
